--- a/resultados/Coordinacion_de_Protecciones/Resultados_Coordinacion_Protecciones.xlsx
+++ b/resultados/Coordinacion_de_Protecciones/Resultados_Coordinacion_Protecciones.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Comparativa_Cabecera_15344" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Aporte_Falla_Generacion" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Conclusion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativa_Cabecera_15344" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aporte_Falla_Generacion" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selectividad_Proyecto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conclusion" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparativa_Cabecera_15344'!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparativa_Cabecera_15344'!$A$1:$I$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -553,12 +554,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Monofasico</t>
+          <t>Bifasico</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>51N/50N (neutro)</t>
+          <t>51/50 (fase)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -567,10 +568,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.112040812952518</v>
+        <v>3.561131837190445</v>
       </c>
       <c r="E4" t="n">
-        <v>4112.040812952519</v>
+        <v>3561.131837190445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -584,12 +585,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Monofasico</t>
+          <t>Bifasico</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>51N/50N (neutro)</t>
+          <t>51/50 (fase)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -598,10 +599,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.1175572044032</v>
+        <v>3.561133266835946</v>
       </c>
       <c r="E5" t="n">
-        <v>4117.5572044032</v>
+        <v>3561.133266835946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -612,14 +613,82 @@
         <v>0.03</v>
       </c>
       <c r="H5" t="n">
-        <v>5.516391450681112</v>
+        <v>0.001429645501048071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1341521570823186</v>
+        <v>4.01458178581782e-05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Monofasico</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>51N/50N (neutro)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CasoBase</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.112040812952518</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4112.040812952519</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Instantaneo</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Monofasico</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>51N/50N (neutro)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Con_Proyecto</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.114801663461343</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4114.801663461342</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Instantaneo</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.760850508823751</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.06714063975550405</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I5"/>
+  <autoFilter ref="A1:I7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -814,7 +883,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Condicion critica evaluada</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Falla trifasica en la barra de 800 V, referida a 13.2 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Corriente de falla referida a 13.2 kV [A]</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Proteccion</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Arranque [A]</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Dial</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>I/Iarranque</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Tiempo de disparo [s]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Proyecto (51, punto de conexion)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Temporizado</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cabecera circuito 15344 (51)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>240</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Temporizado</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.542</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Margen de selectividad [s]</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CUMPLE (&gt;= 0.2 s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Verificacion anti-isla frente al recierre de cabecera</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Recierre rapido de cabecera [s]</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dato EBSA (DOC_REF_EST pag. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Desconexion del proyecto [s]</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Funciones 27/59/81/81R</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Margen antes del recierre [s]</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CUMPLE (&gt;= 0.5 s)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -837,20 +1100,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>- Falla monofasico en cabecera 15344: 4112A -&gt; 4118A (+0.13%), ambos en zona 'Instantaneo' con el mismo tiempo de disparo (0.030s) -&gt; NO requiere reajuste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+          <t>- Falla bifasico en cabecera 15344: 3561A -&gt; 3561A (+0.00%), ambos en zona 'Instantaneo' con el mismo tiempo de disparo (0.030s) -&gt; NO requiere reajuste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>- Falla monofasico en cabecera 15344: 4112A -&gt; 4115A (+0.07%), ambos en zona 'Instantaneo' con el mismo tiempo de disparo (0.030s) -&gt; NO requiere reajuste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Conclusion general</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>No se requiere reajuste de la proteccion de cabecera del circuito 15344: el aporte de falla del proyecto es marginal frente al nivel de cortocircuito de la red de EBSA y ambos escenarios (sin y con proyecto) siguen operando en la misma zona de la curva ya aprobada.</t>
         </is>

--- a/resultados/Coordinacion_de_Protecciones/Resultados_Coordinacion_Protecciones.xlsx
+++ b/resultados/Coordinacion_de_Protecciones/Resultados_Coordinacion_Protecciones.xlsx
@@ -429,7 +429,7 @@
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.561131837190445</v>
+        <v>3.561131837190446</v>
       </c>
       <c r="E4" t="n">
-        <v>3561.131837190445</v>
+        <v>3561.131837190446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.561133266835946</v>
+        <v>3.561133266835948</v>
       </c>
       <c r="E5" t="n">
-        <v>3561.133266835946</v>
+        <v>3561.133266835948</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -613,10 +613,10 @@
         <v>0.03</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001429645501048071</v>
+        <v>0.001429645501957566</v>
       </c>
       <c r="I5" t="n">
-        <v>4.01458178581782e-05</v>
+        <v>4.014581788371768e-05</v>
       </c>
     </row>
     <row r="6">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.112040812952518</v>
+        <v>3.770159792089812</v>
       </c>
       <c r="E6" t="n">
-        <v>4112.040812952519</v>
+        <v>3770.159792089812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.114801663461343</v>
+        <v>3.774327240346848</v>
       </c>
       <c r="E7" t="n">
-        <v>4114.801663461342</v>
+        <v>3774.327240346848</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
         <v>0.03</v>
       </c>
       <c r="H7" t="n">
-        <v>2.760850508823751</v>
+        <v>4.167448257036085</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06714063975550405</v>
+        <v>0.1105377089262854</v>
       </c>
     </row>
   </sheetData>
@@ -1107,7 +1107,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>- Falla monofasico en cabecera 15344: 4112A -&gt; 4115A (+0.07%), ambos en zona 'Instantaneo' con el mismo tiempo de disparo (0.030s) -&gt; NO requiere reajuste.</t>
+          <t>- Falla monofasico en cabecera 15344: 3770A -&gt; 3774A (+0.11%), ambos en zona 'Instantaneo' con el mismo tiempo de disparo (0.030s) -&gt; NO requiere reajuste.</t>
         </is>
       </c>
     </row>

--- a/resultados/Coordinacion_de_Protecciones/Resultados_Coordinacion_Protecciones.xlsx
+++ b/resultados/Coordinacion_de_Protecciones/Resultados_Coordinacion_Protecciones.xlsx
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7146</v>
+        <v>0.7145999999999999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>859</v>
+        <v>858.4</v>
       </c>
     </row>
     <row r="3"/>
@@ -962,7 +962,7 @@
         <v>0.05</v>
       </c>
       <c r="D5" t="n">
-        <v>12.27</v>
+        <v>12.26</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
